--- a/templates_blank/Notas_da_Copa_2026_modelo_PT.xlsx
+++ b/templates_blank/Notas_da_Copa_2026_modelo_PT.xlsx
@@ -4120,7 +4120,7 @@
       </c>
       <c r="E25" s="44" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="F25" s="43" t="n"/>
